--- a/data/trans_orig/P0902-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P0902-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas físicos en 2007</t>
+          <t>Población que dejo de hacer algunas tareas por problemas físicos en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6021</t>
+          <t>5964</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19319</t>
+          <t>20237</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12722</t>
+          <t>12823</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30744</t>
+          <t>30339</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22165</t>
+          <t>20792</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44829</t>
+          <t>44534</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>474745</t>
+          <t>473827</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>488043</t>
+          <t>488100</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>436745</t>
+          <t>437150</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>454767</t>
+          <t>454666</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>916724</t>
+          <t>917019</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>939388</t>
+          <t>940761</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,84%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12215</t>
+          <t>11019</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29758</t>
+          <t>29199</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30534</t>
+          <t>32021</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57098</t>
+          <t>57498</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>47077</t>
+          <t>47079</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>79754</t>
+          <t>81797</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>705731</t>
+          <t>706290</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>723274</t>
+          <t>724470</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>568396</t>
+          <t>567996</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>594960</t>
+          <t>593473</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1281228</t>
+          <t>1279185</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1313905</t>
+          <t>1313903</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20621</t>
+          <t>20409</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41983</t>
+          <t>41347</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44645</t>
+          <t>45085</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>74305</t>
+          <t>74598</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71392</t>
+          <t>69298</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>107948</t>
+          <t>107442</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,09%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>596685</t>
+          <t>597321</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>618047</t>
+          <t>618259</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>615439</t>
+          <t>615146</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>645099</t>
+          <t>644659</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1220464</t>
+          <t>1220970</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1257020</t>
+          <t>1259114</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,78%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24035</t>
+          <t>24837</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47772</t>
+          <t>48141</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51478</t>
+          <t>52059</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82906</t>
+          <t>81745</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>84102</t>
+          <t>82560</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>123514</t>
+          <t>121966</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,79%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>471375</t>
+          <t>471006</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>495112</t>
+          <t>494310</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>432736</t>
+          <t>433897</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>464164</t>
+          <t>463583</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>911275</t>
+          <t>912823</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>950687</t>
+          <t>952229</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>92,02%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>40632</t>
+          <t>39811</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>67918</t>
+          <t>65758</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49613</t>
+          <t>47567</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>79019</t>
+          <t>76872</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>98232</t>
+          <t>95779</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>136285</t>
+          <t>136129</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,22%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>318792</t>
+          <t>320952</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>346078</t>
+          <t>346899</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>324967</t>
+          <t>327114</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>354373</t>
+          <t>356419</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>654411</t>
+          <t>654567</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>692464</t>
+          <t>694917</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,89%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>36789</t>
+          <t>37054</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>61502</t>
+          <t>61951</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>85013</t>
+          <t>85025</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>117746</t>
+          <t>117291</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>128358</t>
+          <t>129197</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>170478</t>
+          <t>170404</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,81%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>231081</t>
+          <t>230632</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>255794</t>
+          <t>255529</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>225188</t>
+          <t>225643</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>257921</t>
+          <t>257909</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>465039</t>
+          <t>465113</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>507159</t>
+          <t>506320</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>79,67%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>58302</t>
+          <t>57297</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>84791</t>
+          <t>85007</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>125231</t>
+          <t>122433</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>161198</t>
+          <t>160771</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>189164</t>
+          <t>191871</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>238597</t>
+          <t>236932</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>43,57%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>125092</t>
+          <t>124876</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>151581</t>
+          <t>152586</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>172710</t>
+          <t>173137</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>208677</t>
+          <t>211475</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>305194</t>
+          <t>306859</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>354627</t>
+          <t>351920</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>56,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>64,72%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>238988</t>
+          <t>238484</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>302230</t>
+          <t>303784</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>451936</t>
+          <t>452227</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>535285</t>
+          <t>533460</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>713886</t>
+          <t>711231</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>816233</t>
+          <t>815883</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2974313</t>
+          <t>2972759</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3037555</t>
+          <t>3038059</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2843912</t>
+          <t>2845737</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2927261</t>
+          <t>2926970</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5839508</t>
+          <t>5839858</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5941855</t>
+          <t>5944510</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,31%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas físicos en 2012</t>
+          <t>Población que dejo de hacer algunas tareas por problemas físicos en 2012 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6630</t>
+          <t>6777</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20195</t>
+          <t>21072</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11603</t>
+          <t>10994</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30233</t>
+          <t>28709</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21829</t>
+          <t>21350</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44979</t>
+          <t>44110</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>433951</t>
+          <t>433074</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>447516</t>
+          <t>447369</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>399997</t>
+          <t>401521</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>418627</t>
+          <t>419236</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>839397</t>
+          <t>840266</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>862547</t>
+          <t>863026</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,59%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13712</t>
+          <t>13819</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33929</t>
+          <t>33581</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20435</t>
+          <t>20487</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42201</t>
+          <t>42984</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39012</t>
+          <t>39061</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>69082</t>
+          <t>69912</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>652237</t>
+          <t>652585</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>672454</t>
+          <t>672347</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>566990</t>
+          <t>566207</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>588756</t>
+          <t>588704</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1226275</t>
+          <t>1225445</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1256345</t>
+          <t>1256296</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,98%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29481</t>
+          <t>29414</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55372</t>
+          <t>55171</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>62587</t>
+          <t>63966</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>98843</t>
+          <t>98991</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>99453</t>
+          <t>100183</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>142953</t>
+          <t>142240</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>626491</t>
+          <t>626692</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>652382</t>
+          <t>652449</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>611038</t>
+          <t>610890</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>647294</t>
+          <t>645915</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1248790</t>
+          <t>1249503</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1292290</t>
+          <t>1291560</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,8%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35937</t>
+          <t>36205</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65366</t>
+          <t>65289</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>76970</t>
+          <t>76265</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>116701</t>
+          <t>112851</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>120250</t>
+          <t>120875</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>168536</t>
+          <t>167769</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>549251</t>
+          <t>549328</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>578680</t>
+          <t>578412</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>499498</t>
+          <t>503348</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>539229</t>
+          <t>539934</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1062280</t>
+          <t>1063047</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1110566</t>
+          <t>1109941</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,18%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>54008</t>
+          <t>53468</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>84043</t>
+          <t>83900</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>105056</t>
+          <t>103289</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>142264</t>
+          <t>143019</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>165854</t>
+          <t>165546</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>215286</t>
+          <t>216906</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,78%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>345386</t>
+          <t>345529</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>375421</t>
+          <t>375961</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>303624</t>
+          <t>302869</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>340832</t>
+          <t>342599</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>660031</t>
+          <t>658411</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>709463</t>
+          <t>709771</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>81,09%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>59470</t>
+          <t>56852</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>91604</t>
+          <t>90042</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>113702</t>
+          <t>114776</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>150264</t>
+          <t>149739</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>179062</t>
+          <t>181338</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>229533</t>
+          <t>228114</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,37%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>218182</t>
+          <t>219744</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>250316</t>
+          <t>252934</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>203732</t>
+          <t>204257</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>240294</t>
+          <t>239220</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>434249</t>
+          <t>435668</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>484720</t>
+          <t>482444</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>72,68%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>95027</t>
+          <t>94899</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>128661</t>
+          <t>128231</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>212710</t>
+          <t>212366</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>252893</t>
+          <t>252000</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>316323</t>
+          <t>318593</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>369682</t>
+          <t>370126</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>57,94%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>121190</t>
+          <t>121620</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>154824</t>
+          <t>154952</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>136086</t>
+          <t>136979</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>176269</t>
+          <t>176613</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>269148</t>
+          <t>268704</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>322507</t>
+          <t>320237</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,13%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>341647</t>
+          <t>338801</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>417602</t>
+          <t>417786</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>665859</t>
+          <t>662615</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>756351</t>
+          <t>760522</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1019635</t>
+          <t>1031353</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1146997</t>
+          <t>1146398</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3008256</t>
+          <t>3008072</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3084211</t>
+          <t>3087057</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2798012</t>
+          <t>2793841</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2888504</t>
+          <t>2891748</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5833225</t>
+          <t>5833824</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5960587</t>
+          <t>5948869</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,22%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas físicos en 2016</t>
+          <t>Población que dejo de hacer algunas tareas por problemas físicos en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2993</t>
+          <t>2982</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15082</t>
+          <t>14258</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6610</t>
+          <t>6671</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20189</t>
+          <t>19764</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12457</t>
+          <t>11531</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29799</t>
+          <t>29071</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>404381</t>
+          <t>405205</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>416470</t>
+          <t>416481</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>375566</t>
+          <t>375991</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>389145</t>
+          <t>389084</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>785419</t>
+          <t>786147</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>802761</t>
+          <t>803687</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13094</t>
+          <t>13154</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31433</t>
+          <t>31520</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19997</t>
+          <t>19986</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41721</t>
+          <t>42111</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37652</t>
+          <t>38715</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>66662</t>
+          <t>68602</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>559063</t>
+          <t>558976</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>577402</t>
+          <t>577342</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>521823</t>
+          <t>521433</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>543547</t>
+          <t>543558</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1087378</t>
+          <t>1085438</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1116388</t>
+          <t>1115325</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19074</t>
+          <t>18600</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40401</t>
+          <t>39010</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37939</t>
+          <t>37099</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65358</t>
+          <t>65294</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61924</t>
+          <t>62470</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>98545</t>
+          <t>97583</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>628696</t>
+          <t>630087</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>650023</t>
+          <t>650497</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>596028</t>
+          <t>596092</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>623447</t>
+          <t>624287</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1231938</t>
+          <t>1232900</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1268559</t>
+          <t>1268013</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,3%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45788</t>
+          <t>44955</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77698</t>
+          <t>75687</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65811</t>
+          <t>66278</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>100648</t>
+          <t>99488</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>118815</t>
+          <t>118988</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>164237</t>
+          <t>165876</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,81%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>568350</t>
+          <t>570361</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>600260</t>
+          <t>601093</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>548429</t>
+          <t>549589</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>583266</t>
+          <t>582799</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1130888</t>
+          <t>1129249</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1176310</t>
+          <t>1176137</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,81%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>45543</t>
+          <t>43531</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>76659</t>
+          <t>76032</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>99162</t>
+          <t>97668</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>140016</t>
+          <t>135828</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>149577</t>
+          <t>149057</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>204966</t>
+          <t>200350</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,55%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>401259</t>
+          <t>401886</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>432375</t>
+          <t>434387</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>356833</t>
+          <t>361021</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>397687</t>
+          <t>399181</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>769801</t>
+          <t>774417</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>825190</t>
+          <t>825710</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>84,71%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>42360</t>
+          <t>42680</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>69504</t>
+          <t>71036</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>104521</t>
+          <t>102807</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>142799</t>
+          <t>141426</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>155679</t>
+          <t>155671</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>202967</t>
+          <t>202870</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8496,7 +8496,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,49%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264826</t>
+          <t>263294</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>291970</t>
+          <t>291650</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>234963</t>
+          <t>236336</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>273241</t>
+          <t>274955</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>509125</t>
+          <t>509222</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>556413</t>
+          <t>556421</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>71462</t>
+          <t>72833</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>99585</t>
+          <t>99387</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>193551</t>
+          <t>194124</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>237504</t>
+          <t>239428</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>274409</t>
+          <t>273338</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>329308</t>
+          <t>329657</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>50,16%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>157413</t>
+          <t>157611</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>185536</t>
+          <t>184165</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>162665</t>
+          <t>160741</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>206618</t>
+          <t>206045</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>327859</t>
+          <t>327510</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>382758</t>
+          <t>383829</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>58,41%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>281101</t>
+          <t>283906</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>349067</t>
+          <t>351962</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>584959</t>
+          <t>582595</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>680069</t>
+          <t>673586</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>884783</t>
+          <t>884720</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1002133</t>
+          <t>1001150</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,43%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3045283</t>
+          <t>3042388</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3113249</t>
+          <t>3110444</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2864473</t>
+          <t>2870956</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2959583</t>
+          <t>2961947</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5936759</t>
+          <t>5937742</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6054109</t>
+          <t>6054172</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,7 +9290,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas físicos en 2023</t>
+          <t>Población que dejo de hacer algunas tareas por problemas físicos en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4435</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5028</t>
+          <t>4350</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28403</t>
+          <t>24368</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4751</t>
+          <t>5042</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27646</t>
+          <t>26184</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>395552</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>284797</t>
+          <t>288832</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>308172</t>
+          <t>308850</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>685541</t>
+          <t>687003</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>708436</t>
+          <t>708145</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19693</t>
+          <t>19044</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48477</t>
+          <t>46828</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11380</t>
+          <t>13536</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36471</t>
+          <t>36109</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37501</t>
+          <t>37723</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>73011</t>
+          <t>74426</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>375070</t>
+          <t>376719</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>403854</t>
+          <t>404503</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>474493</t>
+          <t>474855</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>499584</t>
+          <t>497428</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>861500</t>
+          <t>860085</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>897010</t>
+          <t>896788</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,96%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25519</t>
+          <t>24943</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50494</t>
+          <t>50721</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45951</t>
+          <t>45090</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>69098</t>
+          <t>69369</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>76128</t>
+          <t>76982</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>111015</t>
+          <t>109724</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,17%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>485844</t>
+          <t>485617</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>510819</t>
+          <t>511395</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>473370</t>
+          <t>473099</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>496517</t>
+          <t>497378</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>967791</t>
+          <t>969082</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1002678</t>
+          <t>1001824</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,86%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36712</t>
+          <t>36793</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>126877</t>
+          <t>123509</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>86117</t>
+          <t>86340</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>124277</t>
+          <t>124180</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>105128</t>
+          <t>118009</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>229471</t>
+          <t>234085</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,64%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>759819</t>
+          <t>763187</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>849984</t>
+          <t>849903</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>587971</t>
+          <t>588068</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>626131</t>
+          <t>625908</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1369473</t>
+          <t>1364859</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1493816</t>
+          <t>1480935</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>92,62%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>90717</t>
+          <t>89209</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>126271</t>
+          <t>125916</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>107889</t>
+          <t>108597</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>136761</t>
+          <t>137631</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>207110</t>
+          <t>207881</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>255489</t>
+          <t>256821</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,16%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>434963</t>
+          <t>435318</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>470517</t>
+          <t>472025</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>411144</t>
+          <t>410274</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>440016</t>
+          <t>439308</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>853650</t>
+          <t>852318</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>902029</t>
+          <t>901258</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>81,26%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>50577</t>
+          <t>51044</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>74369</t>
+          <t>74241</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>46794</t>
+          <t>49637</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>178800</t>
+          <t>177995</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>89363</t>
+          <t>89285</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>230530</t>
+          <t>229473</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,53%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>292446</t>
+          <t>292574</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>316238</t>
+          <t>315771</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>79,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>429568</t>
+          <t>430373</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>561574</t>
+          <t>558731</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>744653</t>
+          <t>745710</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>885820</t>
+          <t>885898</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,7 +11583,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>78393</t>
+          <t>79190</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>104475</t>
+          <t>104271</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>218682</t>
+          <t>217436</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>248400</t>
+          <t>247390</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>304039</t>
+          <t>304829</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>343370</t>
+          <t>341551</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>48,27%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>177781</t>
+          <t>177985</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>203863</t>
+          <t>203066</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>71,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>176997</t>
+          <t>178007</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>206715</t>
+          <t>207961</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>364284</t>
+          <t>366103</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>403615</t>
+          <t>402825</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>56,92%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>321017</t>
+          <t>311360</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>460924</t>
+          <t>457551</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>528351</t>
+          <t>539522</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>724086</t>
+          <t>725184</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>929269</t>
+          <t>943159</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1153476</t>
+          <t>1167569</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2995949</t>
+          <t>2999322</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3135856</t>
+          <t>3145513</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2936464</t>
+          <t>2935366</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3132199</t>
+          <t>3121028</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5963947</t>
+          <t>5949854</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6188154</t>
+          <t>6174264</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>86,75%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P0902-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P0902-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5964</t>
+          <t>5546</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20237</t>
+          <t>19326</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12823</t>
+          <t>11544</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30339</t>
+          <t>28408</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20792</t>
+          <t>22268</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44534</t>
+          <t>43774</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>473827</t>
+          <t>474738</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>488100</t>
+          <t>488518</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>437150</t>
+          <t>439081</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>454666</t>
+          <t>455945</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>917019</t>
+          <t>917779</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>940761</t>
+          <t>939285</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11019</t>
+          <t>11309</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29199</t>
+          <t>28904</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32021</t>
+          <t>32548</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57498</t>
+          <t>57863</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>47079</t>
+          <t>47160</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>81797</t>
+          <t>79365</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>706290</t>
+          <t>706585</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>724470</t>
+          <t>724180</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>567996</t>
+          <t>567631</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>593473</t>
+          <t>592946</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1279185</t>
+          <t>1281617</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1313903</t>
+          <t>1313822</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,53%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20409</t>
+          <t>20123</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41347</t>
+          <t>43079</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45085</t>
+          <t>44701</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>74598</t>
+          <t>73000</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>69298</t>
+          <t>69883</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>107442</t>
+          <t>106257</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>597321</t>
+          <t>595589</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>618259</t>
+          <t>618545</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>615146</t>
+          <t>616744</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>644659</t>
+          <t>645043</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1220970</t>
+          <t>1222155</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1259114</t>
+          <t>1258529</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,74%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24837</t>
+          <t>25519</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48141</t>
+          <t>48197</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>52059</t>
+          <t>52087</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81745</t>
+          <t>81380</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>82560</t>
+          <t>82759</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>121966</t>
+          <t>121615</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,75%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>471006</t>
+          <t>470950</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>494310</t>
+          <t>493628</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>433897</t>
+          <t>434262</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>463583</t>
+          <t>463555</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>912823</t>
+          <t>913174</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>952229</t>
+          <t>952030</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,0%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39811</t>
+          <t>40582</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>65758</t>
+          <t>65956</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>47567</t>
+          <t>49438</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>76872</t>
+          <t>77717</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>95779</t>
+          <t>98778</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>136129</t>
+          <t>137835</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,43%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>320952</t>
+          <t>320754</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>346899</t>
+          <t>346128</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>327114</t>
+          <t>326269</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>356419</t>
+          <t>354548</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>654567</t>
+          <t>652861</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>694917</t>
+          <t>691918</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,51%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>37054</t>
+          <t>36156</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>61951</t>
+          <t>60465</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>85025</t>
+          <t>86382</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>117291</t>
+          <t>117647</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>129197</t>
+          <t>130481</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>170404</t>
+          <t>169696</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,7%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>230632</t>
+          <t>232118</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>255529</t>
+          <t>256427</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>225643</t>
+          <t>225287</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>257909</t>
+          <t>256552</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>465113</t>
+          <t>465821</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>506320</t>
+          <t>505036</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>79,47%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>57297</t>
+          <t>59141</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>85007</t>
+          <t>84679</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>122433</t>
+          <t>123998</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>160771</t>
+          <t>160349</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>191871</t>
+          <t>192827</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>236932</t>
+          <t>238264</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>43,82%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>124876</t>
+          <t>125204</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>152586</t>
+          <t>150742</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>173137</t>
+          <t>173559</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>211475</t>
+          <t>209910</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>306859</t>
+          <t>305527</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>351920</t>
+          <t>350964</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>64,54%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>238484</t>
+          <t>239433</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>303784</t>
+          <t>300171</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>452227</t>
+          <t>453785</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>533460</t>
+          <t>535608</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>711231</t>
+          <t>712708</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>815883</t>
+          <t>815514</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,25%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2972759</t>
+          <t>2976372</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3038059</t>
+          <t>3037110</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2845737</t>
+          <t>2843589</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2926970</t>
+          <t>2925412</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5839858</t>
+          <t>5840227</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5944510</t>
+          <t>5943033</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,29%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6777</t>
+          <t>6845</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21072</t>
+          <t>20598</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10994</t>
+          <t>11740</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28709</t>
+          <t>28779</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21350</t>
+          <t>22271</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44110</t>
+          <t>44128</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>433074</t>
+          <t>433548</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>447369</t>
+          <t>447301</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>401521</t>
+          <t>401451</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>419236</t>
+          <t>418490</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>840266</t>
+          <t>840248</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>863026</t>
+          <t>862105</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,48%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13819</t>
+          <t>13460</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33581</t>
+          <t>33291</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20487</t>
+          <t>19825</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42984</t>
+          <t>42188</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39061</t>
+          <t>39748</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>69912</t>
+          <t>69247</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>652585</t>
+          <t>652875</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>672347</t>
+          <t>672706</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>566207</t>
+          <t>567003</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>588704</t>
+          <t>589366</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1225445</t>
+          <t>1226110</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1256296</t>
+          <t>1255609</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,93%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29414</t>
+          <t>30605</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55171</t>
+          <t>57931</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63966</t>
+          <t>61297</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>98991</t>
+          <t>98450</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>100183</t>
+          <t>100290</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>142240</t>
+          <t>143907</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>626692</t>
+          <t>623932</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>652449</t>
+          <t>651258</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>610890</t>
+          <t>611431</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>645915</t>
+          <t>648584</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1249503</t>
+          <t>1247836</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1291560</t>
+          <t>1291453</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,79%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36205</t>
+          <t>36690</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65289</t>
+          <t>63755</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>76265</t>
+          <t>77915</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>112851</t>
+          <t>116068</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>120875</t>
+          <t>121610</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>167769</t>
+          <t>166930</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,56%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>549328</t>
+          <t>550862</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>578412</t>
+          <t>577927</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>503348</t>
+          <t>500131</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>539934</t>
+          <t>538284</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1063047</t>
+          <t>1063886</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1109941</t>
+          <t>1109206</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,12%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>53468</t>
+          <t>54070</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>83900</t>
+          <t>83913</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>103289</t>
+          <t>104263</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>143019</t>
+          <t>142126</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>165546</t>
+          <t>165373</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>216906</t>
+          <t>219020</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>25,02%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>345529</t>
+          <t>345516</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>375961</t>
+          <t>375359</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>302869</t>
+          <t>303762</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>342599</t>
+          <t>341625</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>658411</t>
+          <t>656297</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>709771</t>
+          <t>709944</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>81,11%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>56852</t>
+          <t>58225</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>90042</t>
+          <t>90625</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>114776</t>
+          <t>112886</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>149739</t>
+          <t>151390</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>181338</t>
+          <t>180884</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>228114</t>
+          <t>228895</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,48%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>219744</t>
+          <t>219161</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>252934</t>
+          <t>251561</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>204257</t>
+          <t>202606</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>239220</t>
+          <t>241110</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>435668</t>
+          <t>434887</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>482444</t>
+          <t>482898</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>65,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>72,75%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>94899</t>
+          <t>94945</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>128231</t>
+          <t>127022</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>212366</t>
+          <t>212717</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>252000</t>
+          <t>253482</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>318593</t>
+          <t>315897</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>370126</t>
+          <t>371033</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>49,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>58,08%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>121620</t>
+          <t>122829</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>154952</t>
+          <t>154906</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>62,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>136979</t>
+          <t>135497</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>176613</t>
+          <t>176262</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>268704</t>
+          <t>267797</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>320237</t>
+          <t>322933</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>50,55%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>338801</t>
+          <t>338802</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>417786</t>
+          <t>417195</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>662615</t>
+          <t>659330</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>760522</t>
+          <t>755598</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1031353</t>
+          <t>1025490</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1146398</t>
+          <t>1146875</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,43%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3008072</t>
+          <t>3008663</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3087057</t>
+          <t>3087056</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2793841</t>
+          <t>2798765</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2891748</t>
+          <t>2895033</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5833824</t>
+          <t>5833347</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5948869</t>
+          <t>5954732</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,31%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>3061</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14258</t>
+          <t>16146</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6671</t>
+          <t>6357</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19764</t>
+          <t>20479</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11531</t>
+          <t>12156</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29071</t>
+          <t>29578</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>405205</t>
+          <t>403317</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>416481</t>
+          <t>416402</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>375991</t>
+          <t>375276</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>389084</t>
+          <t>389398</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>786147</t>
+          <t>785640</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>803687</t>
+          <t>803062</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,51%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13154</t>
+          <t>12900</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31520</t>
+          <t>31862</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19986</t>
+          <t>20021</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42111</t>
+          <t>41838</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38715</t>
+          <t>36789</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>68602</t>
+          <t>65922</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>558976</t>
+          <t>558634</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>577342</t>
+          <t>577596</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>521433</t>
+          <t>521706</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>543558</t>
+          <t>543523</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1085438</t>
+          <t>1088118</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1115325</t>
+          <t>1117251</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,81%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18600</t>
+          <t>18728</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39010</t>
+          <t>39278</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37099</t>
+          <t>37357</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65294</t>
+          <t>65942</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62470</t>
+          <t>62906</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>97583</t>
+          <t>98842</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>630087</t>
+          <t>629819</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>650497</t>
+          <t>650369</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>596092</t>
+          <t>595444</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>624287</t>
+          <t>624029</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1232900</t>
+          <t>1231641</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1268013</t>
+          <t>1267577</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,27%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44955</t>
+          <t>46376</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>75687</t>
+          <t>75564</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>66278</t>
+          <t>65932</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>99488</t>
+          <t>101370</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>118988</t>
+          <t>118097</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>165876</t>
+          <t>165213</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,76%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>570361</t>
+          <t>570484</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>601093</t>
+          <t>599672</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>549589</t>
+          <t>547707</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>582799</t>
+          <t>583145</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1129249</t>
+          <t>1129912</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1176137</t>
+          <t>1177028</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,88%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43531</t>
+          <t>42437</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>76032</t>
+          <t>73415</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>97668</t>
+          <t>97058</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>135828</t>
+          <t>135921</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>149057</t>
+          <t>149965</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>200350</t>
+          <t>200564</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,58%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>401886</t>
+          <t>404503</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>434387</t>
+          <t>435481</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>361021</t>
+          <t>360928</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>399181</t>
+          <t>399791</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>774417</t>
+          <t>774203</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>825710</t>
+          <t>824802</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,62%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>42680</t>
+          <t>42904</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>71036</t>
+          <t>69804</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>102807</t>
+          <t>103457</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>141426</t>
+          <t>139859</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>155671</t>
+          <t>155151</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>202870</t>
+          <t>206022</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,93%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>263294</t>
+          <t>264526</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>291650</t>
+          <t>291426</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>236336</t>
+          <t>237903</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>274955</t>
+          <t>274305</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>509222</t>
+          <t>506070</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>556421</t>
+          <t>556941</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>78,21%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>72833</t>
+          <t>71581</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>99387</t>
+          <t>100333</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>194124</t>
+          <t>192688</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>239428</t>
+          <t>237593</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>59,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>273338</t>
+          <t>274072</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>329657</t>
+          <t>329770</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>50,18%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>157611</t>
+          <t>156665</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>184165</t>
+          <t>185417</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>160741</t>
+          <t>162576</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>206045</t>
+          <t>207481</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>327510</t>
+          <t>327397</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>383829</t>
+          <t>383095</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>58,29%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>283906</t>
+          <t>282523</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>351962</t>
+          <t>350229</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>582595</t>
+          <t>578553</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>673586</t>
+          <t>679771</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>884720</t>
+          <t>877351</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1001150</t>
+          <t>1003038</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,46%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3042388</t>
+          <t>3044121</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3110444</t>
+          <t>3111827</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2870956</t>
+          <t>2864771</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2961947</t>
+          <t>2965989</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5937742</t>
+          <t>5935854</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6054172</t>
+          <t>6061541</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,36%</t>
         </is>
       </c>
     </row>
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>12241</t>
+          <t>17735</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4350</t>
+          <t>8185</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24368</t>
+          <t>35487</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>12241</t>
+          <t>17735</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5042</t>
+          <t>8068</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26184</t>
+          <t>35810</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -9778,7 +9778,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>300959</t>
+          <t>344777</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>288832</t>
+          <t>327025</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>308850</t>
+          <t>354327</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>700946</t>
+          <t>752570</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>687003</t>
+          <t>734495</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>708145</t>
+          <t>762237</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30226</t>
+          <t>32057</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19044</t>
+          <t>20092</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46828</t>
+          <t>47514</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>23490</t>
+          <t>25602</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13536</t>
+          <t>16698</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36109</t>
+          <t>37937</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>53716</t>
+          <t>57659</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37723</t>
+          <t>42753</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74426</t>
+          <t>78181</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>393321</t>
+          <t>444833</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>376719</t>
+          <t>429376</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>404503</t>
+          <t>456798</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>487474</t>
+          <t>474902</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>474855</t>
+          <t>462567</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>497428</t>
+          <t>483806</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>880795</t>
+          <t>919735</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>860085</t>
+          <t>899213</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>896788</t>
+          <t>934641</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,63%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>510964</t>
+          <t>500504</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>510964</t>
+          <t>500504</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>510964</t>
+          <t>500504</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>934511</t>
+          <t>977394</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>934511</t>
+          <t>977394</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>934511</t>
+          <t>977394</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>36375</t>
+          <t>37664</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24943</t>
+          <t>27240</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50721</t>
+          <t>53219</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>55804</t>
+          <t>62264</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45090</t>
+          <t>50270</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>69369</t>
+          <t>76119</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>92179</t>
+          <t>99928</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>76982</t>
+          <t>82133</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>109724</t>
+          <t>121087</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>499963</t>
+          <t>583173</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>485617</t>
+          <t>567618</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>511395</t>
+          <t>593597</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>486664</t>
+          <t>559875</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>473099</t>
+          <t>546020</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>497378</t>
+          <t>571869</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>986627</t>
+          <t>1143048</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>969082</t>
+          <t>1121889</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1001824</t>
+          <t>1160843</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>93,39%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>83378</t>
+          <t>91239</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36793</t>
+          <t>72280</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>123509</t>
+          <t>111221</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>102899</t>
+          <t>107914</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>86340</t>
+          <t>91817</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>124180</t>
+          <t>124679</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>186277</t>
+          <t>199153</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>118009</t>
+          <t>174209</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>234085</t>
+          <t>222483</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>15,5%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>803318</t>
+          <t>608274</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>763187</t>
+          <t>588292</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>849903</t>
+          <t>627233</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>609349</t>
+          <t>628329</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>588068</t>
+          <t>611564</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>625908</t>
+          <t>644426</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1412667</t>
+          <t>1236603</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1364859</t>
+          <t>1213273</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1480935</t>
+          <t>1261547</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>87,87%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>886696</t>
+          <t>699513</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>886696</t>
+          <t>699513</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>886696</t>
+          <t>699513</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712248</t>
+          <t>736243</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712248</t>
+          <t>736243</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712248</t>
+          <t>736243</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1598944</t>
+          <t>1435756</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1598944</t>
+          <t>1435756</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1598944</t>
+          <t>1435756</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>107179</t>
+          <t>112481</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>89209</t>
+          <t>94965</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>125916</t>
+          <t>131301</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>122917</t>
+          <t>140069</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>108597</t>
+          <t>124499</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>137631</t>
+          <t>155443</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>230096</t>
+          <t>252550</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>207881</t>
+          <t>226262</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>256821</t>
+          <t>277673</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>22,79%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>454055</t>
+          <t>496865</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>435318</t>
+          <t>478045</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>472025</t>
+          <t>514381</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>424988</t>
+          <t>468786</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>410274</t>
+          <t>453412</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>439308</t>
+          <t>484356</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>879043</t>
+          <t>965652</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>852318</t>
+          <t>940529</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>901258</t>
+          <t>991940</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>81,43%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>61374</t>
+          <t>65879</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51044</t>
+          <t>54927</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>74241</t>
+          <t>79830</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>114141</t>
+          <t>124922</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>49637</t>
+          <t>110398</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>177995</t>
+          <t>138999</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>175515</t>
+          <t>190801</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>89285</t>
+          <t>173188</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>229473</t>
+          <t>209100</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>24,76%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>305441</t>
+          <t>339611</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>292574</t>
+          <t>325660</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>315771</t>
+          <t>350563</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>494227</t>
+          <t>314244</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>430373</t>
+          <t>300167</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>558731</t>
+          <t>328768</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>799668</t>
+          <t>653856</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>745710</t>
+          <t>635557</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>885898</t>
+          <t>671469</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>79,5%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>366815</t>
+          <t>405490</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>366815</t>
+          <t>405490</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>366815</t>
+          <t>405490</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>975183</t>
+          <t>844657</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>975183</t>
+          <t>844657</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>975183</t>
+          <t>844657</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>90973</t>
+          <t>100795</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>79190</t>
+          <t>86542</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>104271</t>
+          <t>115677</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>232036</t>
+          <t>255744</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>217436</t>
+          <t>240512</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>247390</t>
+          <t>272084</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>58,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>323009</t>
+          <t>356539</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>304829</t>
+          <t>335180</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>341551</t>
+          <t>377822</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,82%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>191283</t>
+          <t>208911</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>177985</t>
+          <t>194029</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>203066</t>
+          <t>223164</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>62,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>193361</t>
+          <t>208399</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>178007</t>
+          <t>192059</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>207961</t>
+          <t>223631</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>384645</t>
+          <t>417310</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>366103</t>
+          <t>396027</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>402825</t>
+          <t>438669</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>56,69%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282256</t>
+          <t>309706</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282256</t>
+          <t>309706</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282256</t>
+          <t>309706</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425397</t>
+          <t>464143</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425397</t>
+          <t>464143</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425397</t>
+          <t>464143</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>707654</t>
+          <t>773849</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>707654</t>
+          <t>773849</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>707654</t>
+          <t>773849</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>409505</t>
+          <t>440116</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>311360</t>
+          <t>402461</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>457551</t>
+          <t>481057</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>663528</t>
+          <t>734249</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>539522</t>
+          <t>694929</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>725184</t>
+          <t>774617</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1073033</t>
+          <t>1174366</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>943159</t>
+          <t>1116300</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1167569</t>
+          <t>1233820</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,99%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3047368</t>
+          <t>3089460</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2999322</t>
+          <t>3048519</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3145513</t>
+          <t>3127115</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2997022</t>
+          <t>2999314</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2935366</t>
+          <t>2958946</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3121028</t>
+          <t>3038634</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6044390</t>
+          <t>6088773</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5949854</t>
+          <t>6029319</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6174264</t>
+          <t>6146839</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>84,63%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3456873</t>
+          <t>3529576</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3456873</t>
+          <t>3529576</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3456873</t>
+          <t>3529576</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3660550</t>
+          <t>3733563</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3660550</t>
+          <t>3733563</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3660550</t>
+          <t>3733563</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7117423</t>
+          <t>7263139</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7117423</t>
+          <t>7263139</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7117423</t>
+          <t>7263139</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
